--- a/data/trans_camb/IP1005-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1005-Clase-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,49</t>
+          <t>0,0; 3,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,87</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,91</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,51</t>
+          <t>0,0; 3,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,88</t>
+          <t>0,57; 5,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,31</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,54</t>
+          <t>0,29; 2,67</t>
         </is>
       </c>
     </row>
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,93</t>
+          <t>0,0; 4,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,86</t>
+          <t>0,0; 4,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 2,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,13</t>
+          <t>0,0; 2,46</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,04</t>
+          <t>-0,64; 1,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 2,16</t>
+          <t>-0,31; 2,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,5</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,49</t>
+          <t>-0,47; 0,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 1,33</t>
+          <t>-0,14; 1,23</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 0,0</t>
+          <t>-3,06; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 0,0</t>
+          <t>-2,47; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 0,0</t>
+          <t>-2,74; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 0,0</t>
+          <t>-2,46; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 0,0</t>
+          <t>-2,04; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 0,0</t>
+          <t>-2,23; 0,0</t>
         </is>
       </c>
     </row>
@@ -1421,22 +1421,22 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 0,0</t>
+          <t>-4,66; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 1,65</t>
+          <t>-2,51; 1,66</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 0,0</t>
+          <t>-2,33; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,29</t>
+          <t>-0,82; 1,31</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 0,53</t>
+          <t>-0,33; 0,47</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 0,63</t>
+          <t>-0,24; 0,61</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,39</t>
+          <t>-0,38; 0,38</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 0,95</t>
+          <t>-0,08; 0,99</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,28</t>
+          <t>-0,26; 0,32</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 0,6</t>
+          <t>-0,11; 0,61</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-75,63; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-44,02; 772,05</t>
+          <t>-54,31; 953,37</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1005-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1005-Clase-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,71</t>
+          <t>0,0; 3,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,86</t>
+          <t>0,0; 2,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,19</t>
+          <t>0,56; 4,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,67</t>
+          <t>0,29; 2,52</t>
         </is>
       </c>
     </row>
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,21</t>
+          <t>0,0; 3,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,54</t>
+          <t>0,0; 4,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,24</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,46</t>
+          <t>0,0; 2,77</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,02</t>
+          <t>-0,64; 1,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,15</t>
+          <t>-0,3; 2,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,48</t>
+          <t>-0,32; 0,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 1,23</t>
+          <t>-0,01; 1,4</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 0,0</t>
+          <t>-3,66; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,0</t>
+          <t>-3,0; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 0,0</t>
+          <t>-3,01; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,0</t>
+          <t>-3,0; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 0,0</t>
+          <t>-2,03; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,0</t>
+          <t>-2,13; 0,0</t>
         </is>
       </c>
     </row>
@@ -1421,22 +1421,22 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 0,0</t>
+          <t>-4,16; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 1,66</t>
+          <t>-2,58; 1,67</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 0,0</t>
+          <t>-2,06; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 1,31</t>
+          <t>-0,83; 1,49</t>
         </is>
       </c>
     </row>
@@ -1572,27 +1572,27 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,61</t>
+          <t>-0,27; 0,62</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,38</t>
+          <t>-0,39; 0,38</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 0,99</t>
+          <t>-0,1; 0,91</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,32</t>
+          <t>-0,21; 0,32</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 0,61</t>
+          <t>-0,07; 0,6</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-77,43; 589,57</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-54,31; 953,37</t>
+          <t>-33,0; 859,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1005-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1005-Clase-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,17 +593,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,75</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 1,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -669,17 +669,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,7</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,86</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,48</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,7</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,86</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,7</t>
+          <t>0,0; 3,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,57; 4,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 2,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,52</t>
+          <t>0,29; 2,54</t>
         </is>
       </c>
     </row>
@@ -830,17 +830,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,78</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,9</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,78</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,9</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,22 +943,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,77</t>
+          <t>0,0; 3,13</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,26</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,02</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,72</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,26</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,22 +1099,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 2,09</t>
+          <t>0,0; 1,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,64; 1,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,23</t>
+          <t>-0,28; 2,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 1,4</t>
+          <t>-0,05; 1,33</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>5,52%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>224,4%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,55</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,55</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-0,61</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-0,61</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,55</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,55</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 0,0</t>
+          <t>-2,65; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 0,0</t>
+          <t>-2,75; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 0,0</t>
+          <t>-3,03; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 0,0</t>
+          <t>-3,64; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 0,0</t>
+          <t>-2,18; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,0</t>
+          <t>-2,29; 0,0</t>
         </is>
       </c>
     </row>
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-0,83</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-0,02</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-0,83</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-0,02</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,22; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,52; 1,65</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 0,0</t>
+          <t>-2,04; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,49</t>
+          <t>-0,83; 1,29</t>
         </is>
       </c>
     </row>
@@ -1449,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-2,78%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-2,78%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,0</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0,36</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>0,07</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>0,15</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-0,0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0,36</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,47</t>
+          <t>-0,37; 0,39</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,62</t>
+          <t>-0,1; 0,95</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,38</t>
+          <t>-0,3; 0,53</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 0,91</t>
+          <t>-0,23; 0,63</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,32</t>
+          <t>-0,27; 0,28</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 0,6</t>
+          <t>-0,08; 0,6</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-0,52%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>186,73%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>33,7%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>73,17%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-0,52%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>186,73%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-75,63; —</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-77,43; 589,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-33,0; 859,5</t>
+          <t>-44,02; 772,05</t>
         </is>
       </c>
     </row>
